--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260623.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260623.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,294,007</t>
+          <t>41,502,661</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>41,502,661</t>
+          <t>7,294,007</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>237,662,641</t>
+          <t>23,073,210</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>23,073,210</t>
+          <t>237,662,641</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
